--- a/data/trans_dic/Q23_tabaco_R2-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/Q23_tabaco_R2-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo inicio en el consumo de tabaco fue antes de los 15 años</t>
+          <t>Población cuyo inicio en el consumo de tabaco fue antes de los 15 años (tasa de respuesta: 95,12%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>34,17; 44,61</t>
+          <t>34,66; 44,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>34,82; 43,83</t>
+          <t>35,05; 44,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>36,65; 47,22</t>
+          <t>36,7; 47,08</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>32,35; 43,68</t>
+          <t>32,42; 44,84</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>20,33; 34,31</t>
+          <t>20,84; 33,99</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,76; 28,08</t>
+          <t>16,0; 28,07</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,36; 32,18</t>
+          <t>19,98; 31,85</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12,78; 23,26</t>
+          <t>13,01; 23,52</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>31,35; 39,21</t>
+          <t>31,38; 39,51</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>30,03; 37,2</t>
+          <t>29,68; 37,3</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31,78; 39,96</t>
+          <t>32,18; 40,1</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>26,14; 34,76</t>
+          <t>26,56; 35,13</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>28,99; 37,25</t>
+          <t>28,96; 37,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>30,03; 37,8</t>
+          <t>30,14; 37,95</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33,79; 42,76</t>
+          <t>34,37; 43,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,85; 32,39</t>
+          <t>6,66; 32,66</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,74; 27,16</t>
+          <t>17,12; 26,96</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,49; 32,92</t>
+          <t>23,37; 33,04</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,0; 33,83</t>
+          <t>24,48; 34,28</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>17,34; 26,34</t>
+          <t>17,51; 26,5</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>26,29; 33,12</t>
+          <t>25,69; 32,75</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28,91; 34,67</t>
+          <t>28,85; 34,85</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31,72; 38,19</t>
+          <t>31,38; 38,05</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,75; 28,19</t>
+          <t>9,12; 28,48</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>30,81; 41,34</t>
+          <t>30,69; 41,9</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>31,43; 40,45</t>
+          <t>30,8; 40,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>26,43; 35,8</t>
+          <t>26,77; 35,98</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>26,18; 38,27</t>
+          <t>26,13; 38,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20,21; 32,8</t>
+          <t>19,9; 32,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23,46; 34,25</t>
+          <t>23,6; 34,17</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,95; 27,98</t>
+          <t>18,11; 27,62</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>22,37; 34,07</t>
+          <t>22,32; 33,51</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>28,29; 36,58</t>
+          <t>28,66; 37,48</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>29,56; 36,75</t>
+          <t>29,52; 36,55</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>24,68; 31,32</t>
+          <t>24,49; 31,32</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>26,58; 34,93</t>
+          <t>26,1; 35,44</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>29,31; 37,84</t>
+          <t>29,95; 38,04</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>31,21; 39,58</t>
+          <t>31,07; 39,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28,94; 38,02</t>
+          <t>28,73; 38,05</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>32,03; 41,26</t>
+          <t>31,98; 41,64</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>24,23; 34,16</t>
+          <t>24,35; 34,18</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,96; 34,66</t>
+          <t>25,02; 34,76</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,09; 30,47</t>
+          <t>21,2; 30,25</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>22,82; 31,45</t>
+          <t>23,08; 31,21</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>28,89; 35,24</t>
+          <t>28,99; 35,16</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>30,14; 36,21</t>
+          <t>29,72; 36,27</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>26,97; 33,64</t>
+          <t>26,78; 33,41</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>29,08; 35,72</t>
+          <t>29,24; 35,75</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>33,03; 37,64</t>
+          <t>33,25; 37,82</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>33,61; 37,95</t>
+          <t>33,75; 38,17</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>33,85; 38,42</t>
+          <t>33,83; 38,54</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17,86; 34,95</t>
+          <t>17,78; 35,22</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>23,71; 29,28</t>
+          <t>23,53; 29,28</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,13; 30,47</t>
+          <t>25,15; 30,56</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,54; 28,6</t>
+          <t>23,4; 28,61</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>21,81; 26,61</t>
+          <t>21,64; 26,7</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>30,04; 33,72</t>
+          <t>30,17; 33,8</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30,83; 34,21</t>
+          <t>30,97; 34,39</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29,97; 33,66</t>
+          <t>30,03; 33,63</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>19,82; 30,86</t>
+          <t>19,29; 30,68</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo inicio en el consumo de tabaco fue antes de los 15 años</t>
+          <t>Población cuyo inicio en el consumo de tabaco fue antes de los 15 años (tasa de respuesta: 95,12%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>126211; 164734</t>
+          <t>128022; 166107</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>153310; 192999</t>
+          <t>154318; 195050</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>138197; 178067</t>
+          <t>138385; 177533</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>93805; 126655</t>
+          <t>94013; 129998</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>36376; 61375</t>
+          <t>37284; 60812</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>34818; 62045</t>
+          <t>35354; 62019</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>45706; 72243</t>
+          <t>44860; 71514</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>21581; 39275</t>
+          <t>21973; 39714</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>171867; 214976</t>
+          <t>172019; 216577</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>198576; 246025</t>
+          <t>196289; 246641</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>191168; 240386</t>
+          <t>193616; 241212</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>119926; 159510</t>
+          <t>121852; 161168</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>149756; 192410</t>
+          <t>149576; 192403</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>187115; 235526</t>
+          <t>187774; 236477</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>176349; 223161</t>
+          <t>179353; 224542</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>43333; 205030</t>
+          <t>42179; 206751</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>49465; 75725</t>
+          <t>47746; 75172</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>88838; 124521</t>
+          <t>88398; 124953</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>85995; 121186</t>
+          <t>87708; 122807</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>45045; 68408</t>
+          <t>45466; 68823</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>209117; 263389</t>
+          <t>204357; 260444</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>289429; 347200</t>
+          <t>288916; 348961</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>279181; 336105</t>
+          <t>276150; 334882</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>87032; 251603</t>
+          <t>81419; 254213</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>107078; 143667</t>
+          <t>106666; 145608</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>142933; 183968</t>
+          <t>140090; 186096</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>113186; 153315</t>
+          <t>114634; 154095</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>89100; 130216</t>
+          <t>88927; 129937</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>39020; 63351</t>
+          <t>38423; 61795</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>75420; 110094</t>
+          <t>75870; 109818</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>52719; 82156</t>
+          <t>53171; 81100</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>50911; 77527</t>
+          <t>50784; 76251</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>152960; 197743</t>
+          <t>154934; 202638</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>229459; 285236</t>
+          <t>229154; 283735</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>178190; 226147</t>
+          <t>176837; 226097</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>150935; 198335</t>
+          <t>148200; 201225</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>142946; 184547</t>
+          <t>146065; 185527</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>164214; 208245</t>
+          <t>163478; 209228</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>127805; 167897</t>
+          <t>126893; 168044</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>130177; 167700</t>
+          <t>129964; 169236</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>84224; 118710</t>
+          <t>84640; 118799</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>99062; 137548</t>
+          <t>99272; 137946</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>77628; 112136</t>
+          <t>78041; 111330</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>72475; 99871</t>
+          <t>73284; 99119</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>241296; 294367</t>
+          <t>242129; 293664</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>278191; 334244</t>
+          <t>274290; 334724</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>218334; 272391</t>
+          <t>216843; 270505</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>210503; 258606</t>
+          <t>211718; 258860</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>568525; 647867</t>
+          <t>572225; 650850</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>687193; 775790</t>
+          <t>689918; 780342</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>598752; 679504</t>
+          <t>598347; 681670</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>298145; 583493</t>
+          <t>296898; 587979</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>236687; 292305</t>
+          <t>234941; 292311</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>331091; 401390</t>
+          <t>331337; 402629</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>292931; 355893</t>
+          <t>291263; 356031</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>212404; 259085</t>
+          <t>210736; 259962</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>816937; 916984</t>
+          <t>820550; 919160</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1036339; 1150041</t>
+          <t>1041138; 1156243</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>903152; 1014274</t>
+          <t>904954; 1013420</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>523840; 815602</t>
+          <t>509845; 811062</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/Q23_tabaco_R2-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/Q23_tabaco_R2-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>37,3%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>29,84%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>34,66; 44,98</t>
+          <t>34,3; 44,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>35,05; 44,3</t>
+          <t>35,18; 45,05</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>36,7; 47,08</t>
+          <t>37,29; 47,84</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>32,42; 44,84</t>
+          <t>31,33; 42,8</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>20,84; 33,99</t>
+          <t>20,75; 33,73</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,0; 28,07</t>
+          <t>15,38; 27,37</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,98; 31,85</t>
+          <t>20,29; 31,51</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13,01; 23,52</t>
+          <t>12,16; 22,96</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>31,38; 39,51</t>
+          <t>31,29; 39,84</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>29,68; 37,3</t>
+          <t>29,71; 37,47</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>32,18; 40,1</t>
+          <t>32,22; 40,19</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>26,56; 35,13</t>
+          <t>26,02; 33,88</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>26,72%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>28,96; 37,25</t>
+          <t>29,32; 37,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>30,14; 37,95</t>
+          <t>29,94; 37,85</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34,37; 43,03</t>
+          <t>33,83; 42,53</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,66; 32,66</t>
+          <t>25,73; 35,1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,12; 26,96</t>
+          <t>17,45; 28,18</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,37; 33,04</t>
+          <t>23,42; 33,26</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,48; 34,28</t>
+          <t>24,73; 34,24</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>17,51; 26,5</t>
+          <t>17,64; 26,97</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>25,69; 32,75</t>
+          <t>26,12; 32,56</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28,85; 34,85</t>
+          <t>28,77; 35,06</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31,38; 38,05</t>
+          <t>31,21; 38,03</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,12; 28,48</t>
+          <t>23,74; 30,77</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>29,28%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>30,69; 41,9</t>
+          <t>31,49; 41,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>30,8; 40,92</t>
+          <t>31,08; 41,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>26,77; 35,98</t>
+          <t>27,0; 36,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>26,13; 38,18</t>
+          <t>25,63; 36,43</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19,9; 32,0</t>
+          <t>20,03; 32,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23,6; 34,17</t>
+          <t>23,51; 35,05</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,11; 27,62</t>
+          <t>18,04; 27,61</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>22,32; 33,51</t>
+          <t>21,6; 32,49</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>28,66; 37,48</t>
+          <t>28,61; 36,77</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>29,52; 36,55</t>
+          <t>29,48; 36,64</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>24,49; 31,32</t>
+          <t>24,0; 31,04</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>26,1; 35,44</t>
+          <t>25,7; 33,53</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>36,59%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>31,88%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>29,95; 38,04</t>
+          <t>30,08; 38,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>31,07; 39,76</t>
+          <t>31,09; 39,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28,73; 38,05</t>
+          <t>28,91; 37,95</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31,98; 41,64</t>
+          <t>31,7; 40,7</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>24,35; 34,18</t>
+          <t>24,8; 33,89</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,02; 34,76</t>
+          <t>25,36; 34,86</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,2; 30,25</t>
+          <t>21,6; 30,72</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>23,08; 31,21</t>
+          <t>22,33; 30,69</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>28,99; 35,16</t>
+          <t>28,93; 35,28</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>29,72; 36,27</t>
+          <t>29,98; 36,27</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>26,78; 33,41</t>
+          <t>26,71; 33,28</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>29,24; 35,75</t>
+          <t>28,54; 35,05</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>33,56%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>29,47%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>33,25; 37,82</t>
+          <t>32,97; 37,95</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>33,75; 38,17</t>
+          <t>33,81; 38,15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>33,83; 38,54</t>
+          <t>33,72; 38,39</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17,78; 35,22</t>
+          <t>31,06; 36,06</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>23,53; 29,28</t>
+          <t>23,52; 29,05</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,15; 30,56</t>
+          <t>25,16; 30,37</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,4; 28,61</t>
+          <t>23,78; 28,72</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>21,64; 26,7</t>
+          <t>21,14; 25,94</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>30,17; 33,8</t>
+          <t>30,22; 33,88</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30,97; 34,39</t>
+          <t>31,09; 34,5</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30,03; 33,63</t>
+          <t>30,16; 33,69</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>19,29; 30,68</t>
+          <t>27,68; 31,11</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>110328</t>
+          <t>116540</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>29969</t>
+          <t>30324</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>140297</t>
+          <t>146864</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>128022; 166107</t>
+          <t>126667; 165714</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>154318; 195050</t>
+          <t>154913; 198345</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>138385; 177533</t>
+          <t>140613; 180378</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>94013; 129998</t>
+          <t>97895; 133710</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>37284; 60812</t>
+          <t>37130; 60343</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>35354; 62019</t>
+          <t>33990; 60483</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>44860; 71514</t>
+          <t>45547; 70755</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>21973; 39714</t>
+          <t>21864; 41293</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>172019; 216577</t>
+          <t>171526; 218387</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>196289; 246641</t>
+          <t>196499; 247753</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>193616; 241212</t>
+          <t>193849; 241804</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>121852; 161168</t>
+          <t>128088; 166788</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>120616</t>
+          <t>126822</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>56117</t>
+          <t>61208</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>176733</t>
+          <t>188030</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>149576; 192403</t>
+          <t>151434; 193935</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>187774; 236477</t>
+          <t>186525; 235845</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>179353; 224542</t>
+          <t>176516; 221964</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>42179; 206751</t>
+          <t>108532; 148008</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>47746; 75172</t>
+          <t>48666; 78571</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>88398; 124953</t>
+          <t>88582; 125812</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>87708; 122807</t>
+          <t>88600; 122685</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>45466; 68823</t>
+          <t>49747; 76066</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>204357; 260444</t>
+          <t>207748; 258960</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>288916; 348961</t>
+          <t>288094; 351043</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>276150; 334882</t>
+          <t>274642; 334747</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>81419; 254213</t>
+          <t>167044; 216529</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>108303</t>
+          <t>117424</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>63087</t>
+          <t>67199</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>171391</t>
+          <t>184624</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>106666; 145608</t>
+          <t>109438; 145005</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>140090; 186096</t>
+          <t>141356; 186734</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>114634; 154095</t>
+          <t>115647; 155849</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>88927; 129937</t>
+          <t>96563; 137243</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>38423; 61795</t>
+          <t>38678; 62542</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>75870; 109818</t>
+          <t>75570; 112666</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>53171; 81100</t>
+          <t>52988; 81094</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>50784; 76251</t>
+          <t>54795; 82437</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>154934; 202638</t>
+          <t>154686; 198815</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>229154; 283735</t>
+          <t>228825; 284397</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>176837; 226097</t>
+          <t>173255; 224130</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>148200; 201225</t>
+          <t>162004; 211375</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>148721</t>
+          <t>158217</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>85887</t>
+          <t>89132</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>234609</t>
+          <t>247349</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>146065; 185527</t>
+          <t>146702; 187543</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>163478; 209228</t>
+          <t>163594; 208910</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>126893; 168044</t>
+          <t>127685; 167577</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>129964; 169236</t>
+          <t>138060; 177271</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>84640; 118799</t>
+          <t>86174; 117773</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>99272; 137946</t>
+          <t>100623; 138346</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>78041; 111330</t>
+          <t>79495; 113077</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>73284; 99119</t>
+          <t>76002; 104453</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>242129; 293664</t>
+          <t>241593; 294654</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>274290; 334724</t>
+          <t>276717; 334786</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>216843; 270505</t>
+          <t>216303; 269446</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>211718; 258860</t>
+          <t>221454; 271979</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>487969</t>
+          <t>519004</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>235060</t>
+          <t>247863</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>723029</t>
+          <t>766867</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>572225; 650850</t>
+          <t>567441; 653171</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>689918; 780342</t>
+          <t>691164; 779873</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>598347; 681670</t>
+          <t>596422; 678993</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>296898; 587979</t>
+          <t>480345; 557676</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>234941; 292311</t>
+          <t>234847; 290074</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>331337; 402629</t>
+          <t>331478; 400047</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>291263; 356031</t>
+          <t>295955; 357459</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>210736; 259962</t>
+          <t>223224; 273858</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>820550; 919160</t>
+          <t>821881; 921289</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1041138; 1156243</t>
+          <t>1045128; 1159739</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>904954; 1013420</t>
+          <t>908851; 1015207</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>509845; 811062</t>
+          <t>720426; 809577</t>
         </is>
       </c>
     </row>
